--- a/data/trans_orig/IP41-Clase-trans_orig.xlsx
+++ b/data/trans_orig/IP41-Clase-trans_orig.xlsx
@@ -543,7 +543,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -554,7 +554,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -727,67 +727,67 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
+          <t>90784</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>85925</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>93642</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>93,66%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>88,64%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>96,61%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>136</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
           <t>92161</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>86063</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>96316</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>86590</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>96900</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>89,73%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>83,79%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>93,77%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>136</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>90784</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>85973</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>93634</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>93,66%</t>
-        </is>
-      </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>88,69%</t>
+          <t>84,3%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>96,6%</t>
+          <t>94,34%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -802,12 +802,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>175338</t>
+          <t>175509</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>188396</t>
+          <t>188492</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -817,12 +817,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>87,82%</t>
+          <t>87,91%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>94,37%</t>
+          <t>94,41%</t>
         </is>
       </c>
     </row>
@@ -835,72 +835,72 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>6148</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>3290</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>11007</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>6,34%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>3,39%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>11,36%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>15</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>10553</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>6398</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>16651</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>5814</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>16124</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>10,27%</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>6,23%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>16,21%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>6148</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>3298</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>10959</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>6,34%</t>
-        </is>
-      </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>3,4%</t>
+          <t>5,66%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>11,31%</t>
+          <t>15,7%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -915,12 +915,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>11249</t>
+          <t>11153</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>24307</t>
+          <t>24136</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -930,12 +930,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>5,63%</t>
+          <t>5,59%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>12,18%</t>
+          <t>12,09%</t>
         </is>
       </c>
     </row>
@@ -948,57 +948,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>145</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>96932</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>96932</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>96932</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>151</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>102714</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
         <is>
           <t>102714</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="M6" s="2" t="inlineStr">
         <is>
           <t>102714</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>145</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>96932</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>96932</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>96932</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1065,72 +1065,72 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>123</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>81685</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>77490</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>84140</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>95,02%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>90,14%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>97,87%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>119</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="K7" s="2" t="inlineStr">
         <is>
           <t>79849</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>74316</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>83003</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>75244</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>83359</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
         <is>
           <t>92,77%</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>86,34%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>96,44%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>123</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>81685</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>77980</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>84119</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>95,02%</t>
-        </is>
-      </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>90,71%</t>
+          <t>87,42%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>97,85%</t>
+          <t>96,85%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1145,12 +1145,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>155888</t>
+          <t>156299</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>166120</t>
+          <t>166141</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1160,12 +1160,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>90,61%</t>
+          <t>90,85%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>96,56%</t>
+          <t>96,57%</t>
         </is>
       </c>
     </row>
@@ -1178,72 +1178,72 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>4285</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>1830</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>8480</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>4,98%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>2,13%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>9,86%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>9</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>6221</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>3067</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>11754</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>2711</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>10826</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
         <is>
           <t>7,23%</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>3,56%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>13,66%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>4285</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>1851</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>7990</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>4,98%</t>
-        </is>
-      </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>2,15%</t>
+          <t>3,15%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>9,29%</t>
+          <t>12,58%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1258,12 +1258,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>5920</t>
+          <t>5899</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>16152</t>
+          <t>15741</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1273,12 +1273,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>3,44%</t>
+          <t>3,43%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>9,39%</t>
+          <t>9,15%</t>
         </is>
       </c>
     </row>
@@ -1291,57 +1291,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>130</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>85970</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>85970</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>85970</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>128</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>86070</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
         <is>
           <t>86070</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="M9" s="2" t="inlineStr">
         <is>
           <t>86070</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>130</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>85970</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>85970</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>85970</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1408,74 +1408,74 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>136</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>90767</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>85094</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>94439</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>91,38%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>85,67%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>95,07%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>98</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="K10" s="2" t="inlineStr">
         <is>
           <t>64960</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>60363</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>60117</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
         <is>
           <t>66676</t>
         </is>
       </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>96,39%</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>89,57%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
+      <c r="O10" s="2" t="inlineStr">
+        <is>
+          <t>89,21%</t>
+        </is>
+      </c>
+      <c r="P10" s="2" t="inlineStr">
         <is>
           <t>98,94%</t>
         </is>
       </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>136</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>90767</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>84900</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>94519</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>91,38%</t>
-        </is>
-      </c>
-      <c r="O10" s="2" t="inlineStr">
-        <is>
-          <t>85,47%</t>
-        </is>
-      </c>
-      <c r="P10" s="2" t="inlineStr">
-        <is>
-          <t>95,15%</t>
-        </is>
-      </c>
       <c r="Q10" s="2" t="inlineStr">
         <is>
           <t>234</t>
@@ -1488,12 +1488,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>149476</t>
+          <t>149377</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>160963</t>
+          <t>160122</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1503,12 +1503,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>89,66%</t>
+          <t>89,6%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>96,54%</t>
+          <t>96,04%</t>
         </is>
       </c>
     </row>
@@ -1521,72 +1521,72 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>8565</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>4893</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>14238</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>8,62%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>4,93%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>14,33%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>2432</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
+      <c r="L11" s="2" t="inlineStr">
         <is>
           <t>716</t>
         </is>
       </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>7029</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>7275</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
         <is>
           <t>3,61%</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
+      <c r="O11" s="2" t="inlineStr">
         <is>
           <t>1,06%</t>
         </is>
       </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>10,43%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>8565</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>4813</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>14432</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>8,62%</t>
-        </is>
-      </c>
-      <c r="O11" s="2" t="inlineStr">
-        <is>
-          <t>4,85%</t>
-        </is>
-      </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>14,53%</t>
+          <t>10,79%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1601,12 +1601,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>5761</t>
+          <t>6602</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>17248</t>
+          <t>17347</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1616,12 +1616,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>3,46%</t>
+          <t>3,96%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>10,34%</t>
+          <t>10,4%</t>
         </is>
       </c>
     </row>
@@ -1634,57 +1634,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>148</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>99332</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>99332</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>99332</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>101</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>67392</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
         <is>
           <t>67392</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="M12" s="2" t="inlineStr">
         <is>
           <t>67392</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>148</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>99332</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>99332</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>99332</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1751,72 +1751,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>269</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>178927</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>171556</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>185345</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>89,99%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>86,28%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>93,21%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>272</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="K13" s="2" t="inlineStr">
         <is>
           <t>179986</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>172415</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>185926</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>172005</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>185990</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>90,55%</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>86,74%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>93,54%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>269</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>178927</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>170823</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>185039</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>89,99%</t>
-        </is>
-      </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>85,91%</t>
+          <t>86,53%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>93,06%</t>
+          <t>93,57%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1831,12 +1831,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>348734</t>
+          <t>348145</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>367961</t>
+          <t>368017</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1846,12 +1846,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>87,71%</t>
+          <t>87,56%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>92,54%</t>
+          <t>92,56%</t>
         </is>
       </c>
     </row>
@@ -1864,72 +1864,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>19914</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>13496</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>27285</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>10,01%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>6,79%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>13,72%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>28</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>18785</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>12845</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>26356</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>12781</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>26766</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>9,45%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>6,46%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>13,26%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>19914</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>13802</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>28018</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>10,01%</t>
-        </is>
-      </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>6,94%</t>
+          <t>6,43%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>14,09%</t>
+          <t>13,47%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1944,12 +1944,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>29651</t>
+          <t>29595</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>48878</t>
+          <t>49467</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1959,12 +1959,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>7,46%</t>
+          <t>7,44%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>12,29%</t>
+          <t>12,44%</t>
         </is>
       </c>
     </row>
@@ -1977,57 +1977,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>299</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>198841</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>198841</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>198841</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>300</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>198771</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>198771</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>198771</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>299</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>198841</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>198841</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>198841</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2094,72 +2094,72 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>177</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>117302</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>111712</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>120812</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>93,54%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>89,08%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>96,34%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>133</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="K16" s="2" t="inlineStr">
         <is>
           <t>88991</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>83174</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>93843</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>82538</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>93177</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
         <is>
           <t>87,92%</t>
         </is>
       </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>82,18%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>92,72%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>177</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t>117302</t>
-        </is>
-      </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>111322</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>120850</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
-        <is>
-          <t>93,54%</t>
-        </is>
-      </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>88,77%</t>
+          <t>81,55%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>96,37%</t>
+          <t>92,06%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2174,12 +2174,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>198941</t>
+          <t>199299</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>212756</t>
+          <t>212350</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2189,12 +2189,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>87,79%</t>
+          <t>87,95%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>93,89%</t>
+          <t>93,71%</t>
         </is>
       </c>
     </row>
@@ -2207,72 +2207,72 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>8098</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>4588</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>13688</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>6,46%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>3,66%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>10,92%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>19</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="K17" s="2" t="inlineStr">
         <is>
           <t>12222</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>7370</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>18039</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>8036</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>18675</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
         <is>
           <t>12,08%</t>
         </is>
       </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>7,28%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>17,82%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>8098</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>4550</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>14078</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
-        <is>
-          <t>6,46%</t>
-        </is>
-      </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>3,63%</t>
+          <t>7,94%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>11,23%</t>
+          <t>18,45%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2287,12 +2287,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>13857</t>
+          <t>14263</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>27672</t>
+          <t>27314</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2302,12 +2302,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>6,11%</t>
+          <t>6,29%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>12,21%</t>
+          <t>12,05%</t>
         </is>
       </c>
     </row>
@@ -2320,57 +2320,57 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>189</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>125400</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>125400</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>125400</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>152</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="K18" s="2" t="inlineStr">
         <is>
           <t>101213</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
+      <c r="L18" s="2" t="inlineStr">
         <is>
           <t>101213</t>
         </is>
       </c>
-      <c r="F18" s="2" t="inlineStr">
+      <c r="M18" s="2" t="inlineStr">
         <is>
           <t>101213</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>189</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="inlineStr">
-        <is>
-          <t>125400</t>
-        </is>
-      </c>
-      <c r="L18" s="2" t="inlineStr">
-        <is>
-          <t>125400</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="inlineStr">
-        <is>
-          <t>125400</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2437,72 +2437,72 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
+          <t>97</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>64900</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>60103</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>68044</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>89,65%</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>83,02%</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>93,99%</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr">
+        <is>
           <t>99</t>
         </is>
       </c>
-      <c r="D19" s="2" t="inlineStr">
+      <c r="K19" s="2" t="inlineStr">
         <is>
           <t>67286</t>
         </is>
       </c>
-      <c r="E19" s="2" t="inlineStr">
-        <is>
-          <t>62163</t>
-        </is>
-      </c>
-      <c r="F19" s="2" t="inlineStr">
-        <is>
-          <t>70758</t>
-        </is>
-      </c>
-      <c r="G19" s="2" t="inlineStr">
+      <c r="L19" s="2" t="inlineStr">
+        <is>
+          <t>61881</t>
+        </is>
+      </c>
+      <c r="M19" s="2" t="inlineStr">
+        <is>
+          <t>70747</t>
+        </is>
+      </c>
+      <c r="N19" s="2" t="inlineStr">
         <is>
           <t>89,87%</t>
         </is>
       </c>
-      <c r="H19" s="2" t="inlineStr">
-        <is>
-          <t>83,03%</t>
-        </is>
-      </c>
-      <c r="I19" s="2" t="inlineStr">
-        <is>
-          <t>94,51%</t>
-        </is>
-      </c>
-      <c r="J19" s="2" t="inlineStr">
-        <is>
-          <t>97</t>
-        </is>
-      </c>
-      <c r="K19" s="2" t="inlineStr">
-        <is>
-          <t>64900</t>
-        </is>
-      </c>
-      <c r="L19" s="2" t="inlineStr">
-        <is>
-          <t>59936</t>
-        </is>
-      </c>
-      <c r="M19" s="2" t="inlineStr">
-        <is>
-          <t>68039</t>
-        </is>
-      </c>
-      <c r="N19" s="2" t="inlineStr">
-        <is>
-          <t>89,65%</t>
-        </is>
-      </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>82,79%</t>
+          <t>82,65%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>93,99%</t>
+          <t>94,49%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2517,12 +2517,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>125294</t>
+          <t>125145</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>137436</t>
+          <t>137145</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2532,12 +2532,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>85,08%</t>
+          <t>84,98%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>93,33%</t>
+          <t>93,13%</t>
         </is>
       </c>
     </row>
@@ -2550,72 +2550,72 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>7492</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>4348</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>12289</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>10,35%</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>6,01%</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>16,98%</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr">
+        <is>
           <t>11</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
+      <c r="K20" s="2" t="inlineStr">
         <is>
           <t>7584</t>
         </is>
       </c>
-      <c r="E20" s="2" t="inlineStr">
-        <is>
-          <t>4112</t>
-        </is>
-      </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>12707</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="inlineStr">
+      <c r="L20" s="2" t="inlineStr">
+        <is>
+          <t>4123</t>
+        </is>
+      </c>
+      <c r="M20" s="2" t="inlineStr">
+        <is>
+          <t>12989</t>
+        </is>
+      </c>
+      <c r="N20" s="2" t="inlineStr">
         <is>
           <t>10,13%</t>
         </is>
       </c>
-      <c r="H20" s="2" t="inlineStr">
-        <is>
-          <t>5,49%</t>
-        </is>
-      </c>
-      <c r="I20" s="2" t="inlineStr">
-        <is>
-          <t>16,97%</t>
-        </is>
-      </c>
-      <c r="J20" s="2" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="K20" s="2" t="inlineStr">
-        <is>
-          <t>7492</t>
-        </is>
-      </c>
-      <c r="L20" s="2" t="inlineStr">
-        <is>
-          <t>4353</t>
-        </is>
-      </c>
-      <c r="M20" s="2" t="inlineStr">
-        <is>
-          <t>12456</t>
-        </is>
-      </c>
-      <c r="N20" s="2" t="inlineStr">
-        <is>
-          <t>10,35%</t>
-        </is>
-      </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>6,01%</t>
+          <t>5,51%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>17,21%</t>
+          <t>17,35%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2630,12 +2630,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>9826</t>
+          <t>10117</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>21968</t>
+          <t>22117</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2645,12 +2645,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>6,67%</t>
+          <t>6,87%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>14,92%</t>
+          <t>15,02%</t>
         </is>
       </c>
     </row>
@@ -2663,57 +2663,57 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
+          <t>109</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>72392</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>72392</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>72392</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="inlineStr">
+        <is>
           <t>110</t>
         </is>
       </c>
-      <c r="D21" s="2" t="inlineStr">
+      <c r="K21" s="2" t="inlineStr">
         <is>
           <t>74870</t>
         </is>
       </c>
-      <c r="E21" s="2" t="inlineStr">
+      <c r="L21" s="2" t="inlineStr">
         <is>
           <t>74870</t>
         </is>
       </c>
-      <c r="F21" s="2" t="inlineStr">
+      <c r="M21" s="2" t="inlineStr">
         <is>
           <t>74870</t>
-        </is>
-      </c>
-      <c r="G21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J21" s="2" t="inlineStr">
-        <is>
-          <t>109</t>
-        </is>
-      </c>
-      <c r="K21" s="2" t="inlineStr">
-        <is>
-          <t>72392</t>
-        </is>
-      </c>
-      <c r="L21" s="2" t="inlineStr">
-        <is>
-          <t>72392</t>
-        </is>
-      </c>
-      <c r="M21" s="2" t="inlineStr">
-        <is>
-          <t>72392</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2780,72 +2780,72 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
+          <t>938</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>624365</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>610993</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>634262</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t>91,97%</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t>90,0%</t>
+        </is>
+      </c>
+      <c r="I22" s="2" t="inlineStr">
+        <is>
+          <t>93,43%</t>
+        </is>
+      </c>
+      <c r="J22" s="2" t="inlineStr">
+        <is>
           <t>857</t>
         </is>
       </c>
-      <c r="D22" s="2" t="inlineStr">
+      <c r="K22" s="2" t="inlineStr">
         <is>
           <t>573234</t>
         </is>
       </c>
-      <c r="E22" s="2" t="inlineStr">
-        <is>
-          <t>560168</t>
-        </is>
-      </c>
-      <c r="F22" s="2" t="inlineStr">
-        <is>
-          <t>584716</t>
-        </is>
-      </c>
-      <c r="G22" s="2" t="inlineStr">
+      <c r="L22" s="2" t="inlineStr">
+        <is>
+          <t>560509</t>
+        </is>
+      </c>
+      <c r="M22" s="2" t="inlineStr">
+        <is>
+          <t>584099</t>
+        </is>
+      </c>
+      <c r="N22" s="2" t="inlineStr">
         <is>
           <t>90,84%</t>
         </is>
       </c>
-      <c r="H22" s="2" t="inlineStr">
-        <is>
-          <t>88,77%</t>
-        </is>
-      </c>
-      <c r="I22" s="2" t="inlineStr">
-        <is>
-          <t>92,66%</t>
-        </is>
-      </c>
-      <c r="J22" s="2" t="inlineStr">
-        <is>
-          <t>938</t>
-        </is>
-      </c>
-      <c r="K22" s="2" t="inlineStr">
-        <is>
-          <t>624365</t>
-        </is>
-      </c>
-      <c r="L22" s="2" t="inlineStr">
-        <is>
-          <t>612473</t>
-        </is>
-      </c>
-      <c r="M22" s="2" t="inlineStr">
-        <is>
-          <t>634932</t>
-        </is>
-      </c>
-      <c r="N22" s="2" t="inlineStr">
-        <is>
-          <t>91,97%</t>
-        </is>
-      </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>90,22%</t>
+          <t>88,82%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>93,53%</t>
+          <t>92,56%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2860,12 +2860,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>1181855</t>
+          <t>1180612</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>1213586</t>
+          <t>1214361</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2875,12 +2875,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>90,23%</t>
+          <t>90,13%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>92,65%</t>
+          <t>92,71%</t>
         </is>
       </c>
     </row>
@@ -2893,72 +2893,72 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
+          <t>82</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>54502</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>44605</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>67874</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>8,03%</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>6,57%</t>
+        </is>
+      </c>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t>10,0%</t>
+        </is>
+      </c>
+      <c r="J23" s="2" t="inlineStr">
+        <is>
           <t>85</t>
         </is>
       </c>
-      <c r="D23" s="2" t="inlineStr">
+      <c r="K23" s="2" t="inlineStr">
         <is>
           <t>57796</t>
         </is>
       </c>
-      <c r="E23" s="2" t="inlineStr">
-        <is>
-          <t>46314</t>
-        </is>
-      </c>
-      <c r="F23" s="2" t="inlineStr">
-        <is>
-          <t>70862</t>
-        </is>
-      </c>
-      <c r="G23" s="2" t="inlineStr">
+      <c r="L23" s="2" t="inlineStr">
+        <is>
+          <t>46931</t>
+        </is>
+      </c>
+      <c r="M23" s="2" t="inlineStr">
+        <is>
+          <t>70521</t>
+        </is>
+      </c>
+      <c r="N23" s="2" t="inlineStr">
         <is>
           <t>9,16%</t>
         </is>
       </c>
-      <c r="H23" s="2" t="inlineStr">
-        <is>
-          <t>7,34%</t>
-        </is>
-      </c>
-      <c r="I23" s="2" t="inlineStr">
-        <is>
-          <t>11,23%</t>
-        </is>
-      </c>
-      <c r="J23" s="2" t="inlineStr">
-        <is>
-          <t>82</t>
-        </is>
-      </c>
-      <c r="K23" s="2" t="inlineStr">
-        <is>
-          <t>54502</t>
-        </is>
-      </c>
-      <c r="L23" s="2" t="inlineStr">
-        <is>
-          <t>43935</t>
-        </is>
-      </c>
-      <c r="M23" s="2" t="inlineStr">
-        <is>
-          <t>66394</t>
-        </is>
-      </c>
-      <c r="N23" s="2" t="inlineStr">
-        <is>
-          <t>8,03%</t>
-        </is>
-      </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>6,47%</t>
+          <t>7,44%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>9,78%</t>
+          <t>11,18%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2973,12 +2973,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>96311</t>
+          <t>95536</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>128042</t>
+          <t>129285</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2988,12 +2988,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>7,35%</t>
+          <t>7,29%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>9,77%</t>
+          <t>9,87%</t>
         </is>
       </c>
     </row>
@@ -3006,57 +3006,57 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
+          <t>1020</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>678867</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>678867</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>678867</t>
+        </is>
+      </c>
+      <c r="G24" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H24" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I24" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J24" s="2" t="inlineStr">
+        <is>
           <t>942</t>
         </is>
       </c>
-      <c r="D24" s="2" t="inlineStr">
+      <c r="K24" s="2" t="inlineStr">
         <is>
           <t>631030</t>
         </is>
       </c>
-      <c r="E24" s="2" t="inlineStr">
+      <c r="L24" s="2" t="inlineStr">
         <is>
           <t>631030</t>
         </is>
       </c>
-      <c r="F24" s="2" t="inlineStr">
+      <c r="M24" s="2" t="inlineStr">
         <is>
           <t>631030</t>
-        </is>
-      </c>
-      <c r="G24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J24" s="2" t="inlineStr">
-        <is>
-          <t>1020</t>
-        </is>
-      </c>
-      <c r="K24" s="2" t="inlineStr">
-        <is>
-          <t>678867</t>
-        </is>
-      </c>
-      <c r="L24" s="2" t="inlineStr">
-        <is>
-          <t>678867</t>
-        </is>
-      </c>
-      <c r="M24" s="2" t="inlineStr">
-        <is>
-          <t>678867</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3178,7 +3178,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -3189,7 +3189,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -3357,72 +3357,72 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>123</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>84932</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>80032</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>87686</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>94,62%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>89,16%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>97,69%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>122</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
         <is>
           <t>84062</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>78530</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>87214</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>79079</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>87089</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>93,47%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>87,32%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>96,98%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>123</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>84932</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>80130</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>87724</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>94,62%</t>
-        </is>
-      </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>89,27%</t>
+          <t>87,93%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>97,73%</t>
+          <t>96,84%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -3437,12 +3437,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>162941</t>
+          <t>162861</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>173180</t>
+          <t>173650</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -3452,12 +3452,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>90,68%</t>
+          <t>90,63%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>96,37%</t>
+          <t>96,63%</t>
         </is>
       </c>
     </row>
@@ -3470,72 +3470,72 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>4831</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>2077</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>9731</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>5,38%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>2,31%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>10,84%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>8</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>5871</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>2719</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>11403</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>2844</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>10854</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>6,53%</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>3,02%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>12,68%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>4831</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>2039</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>9633</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>5,38%</t>
-        </is>
-      </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>2,27%</t>
+          <t>3,16%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>10,73%</t>
+          <t>12,07%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -3550,12 +3550,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>6517</t>
+          <t>6047</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>16756</t>
+          <t>16836</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -3565,12 +3565,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>3,63%</t>
+          <t>3,37%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>9,32%</t>
+          <t>9,37%</t>
         </is>
       </c>
     </row>
@@ -3588,52 +3588,52 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
+          <t>89763</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>89763</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>89763</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
+          <t>130</t>
+        </is>
+      </c>
+      <c r="K6" s="2" t="inlineStr">
+        <is>
           <t>89933</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
         <is>
           <t>89933</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="M6" s="2" t="inlineStr">
         <is>
           <t>89933</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>130</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>89763</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>89763</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>89763</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -3700,72 +3700,72 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>124</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>85987</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>80365</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>90295</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>88,85%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>83,04%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>93,3%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>122</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="K7" s="2" t="inlineStr">
         <is>
           <t>83467</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>77967</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>87753</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>77266</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>87613</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
         <is>
           <t>89,49%</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>83,6%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>94,09%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>124</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>85987</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>79661</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>90109</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>88,85%</t>
-        </is>
-      </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>82,31%</t>
+          <t>82,85%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>93,11%</t>
+          <t>93,94%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -3780,12 +3780,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>160631</t>
+          <t>161897</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>175732</t>
+          <t>175942</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -3795,12 +3795,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>84,52%</t>
+          <t>85,19%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>92,47%</t>
+          <t>92,58%</t>
         </is>
       </c>
     </row>
@@ -3813,72 +3813,72 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>10791</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>6483</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>16413</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>11,15%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>6,7%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>16,96%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>14</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>9799</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>5513</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>15299</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>5653</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>16000</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
         <is>
           <t>10,51%</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>5,91%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>16,4%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>10791</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>6669</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>17117</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>11,15%</t>
-        </is>
-      </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>6,89%</t>
+          <t>6,06%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>17,69%</t>
+          <t>17,15%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -3893,12 +3893,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>14312</t>
+          <t>14102</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>29413</t>
+          <t>28147</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -3908,12 +3908,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>7,53%</t>
+          <t>7,42%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>15,48%</t>
+          <t>14,81%</t>
         </is>
       </c>
     </row>
@@ -3926,57 +3926,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>140</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>96778</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>96778</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>96778</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>136</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>93266</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
         <is>
           <t>93266</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="M9" s="2" t="inlineStr">
         <is>
           <t>93266</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>140</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>96778</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>96778</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>96778</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -4043,72 +4043,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>117</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>81183</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>75950</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>84449</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>93,43%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>87,41%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>97,19%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>118</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="K10" s="2" t="inlineStr">
         <is>
           <t>80564</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>75604</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>83371</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>75860</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>83424</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>93,51%</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>87,75%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>96,77%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>117</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>81183</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>76362</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>84228</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>93,43%</t>
-        </is>
-      </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>87,88%</t>
+          <t>88,05%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>96,94%</t>
+          <t>96,83%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4123,12 +4123,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>155017</t>
+          <t>155676</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>166196</t>
+          <t>166601</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4138,12 +4138,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>89,58%</t>
+          <t>89,96%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>96,04%</t>
+          <t>96,28%</t>
         </is>
       </c>
     </row>
@@ -4161,67 +4161,67 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
+          <t>5707</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>2441</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>10940</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>6,57%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>2,81%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>12,59%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="K11" s="2" t="inlineStr">
+        <is>
           <t>5593</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>2786</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>10553</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>2733</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>10297</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
         <is>
           <t>6,49%</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>3,23%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>12,25%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>5707</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>2662</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>10528</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>6,57%</t>
-        </is>
-      </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>3,06%</t>
+          <t>3,17%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>12,12%</t>
+          <t>11,95%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4236,12 +4236,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>6851</t>
+          <t>6446</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>18030</t>
+          <t>17371</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4251,12 +4251,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>3,96%</t>
+          <t>3,72%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>10,42%</t>
+          <t>10,04%</t>
         </is>
       </c>
     </row>
@@ -4269,57 +4269,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>125</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>86890</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>86890</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>86890</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>126</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>86157</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
         <is>
           <t>86157</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="M12" s="2" t="inlineStr">
         <is>
           <t>86157</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>125</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>86890</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>86890</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>86890</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -4386,72 +4386,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>280</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>196870</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>188404</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>204997</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>86,31%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>82,59%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>89,87%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>264</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="K13" s="2" t="inlineStr">
         <is>
           <t>182457</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>173510</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>188475</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>173227</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>189121</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>88,52%</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>84,18%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>91,44%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>280</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>196870</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>187614</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>205505</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>86,31%</t>
-        </is>
-      </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>82,25%</t>
+          <t>84,05%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>90,09%</t>
+          <t>91,76%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -4466,12 +4466,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>365590</t>
+          <t>367335</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>389060</t>
+          <t>390821</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -4481,12 +4481,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>84,2%</t>
+          <t>84,6%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>89,6%</t>
+          <t>90,01%</t>
         </is>
       </c>
     </row>
@@ -4499,72 +4499,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>44</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>31236</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>23109</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>39702</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>13,69%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>10,13%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>17,41%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>35</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>23651</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>17633</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>32598</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>16987</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>32881</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>11,48%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>8,56%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>15,82%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>44</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>31236</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>22601</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>40492</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>13,69%</t>
-        </is>
-      </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>9,91%</t>
+          <t>8,24%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>17,75%</t>
+          <t>15,95%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -4579,12 +4579,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>45153</t>
+          <t>43392</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>68623</t>
+          <t>66878</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -4594,12 +4594,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>10,4%</t>
+          <t>9,99%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>15,8%</t>
+          <t>15,4%</t>
         </is>
       </c>
     </row>
@@ -4612,57 +4612,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>324</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>228106</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>228106</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>228106</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>299</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>206108</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>206108</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>206108</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>324</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>228106</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>228106</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>228106</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -4729,72 +4729,72 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>164</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>117876</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>109742</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>124261</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>83,57%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>77,8%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>88,09%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>176</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="K16" s="2" t="inlineStr">
         <is>
           <t>123820</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>115234</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>130014</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>115509</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>130793</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
         <is>
           <t>83,01%</t>
         </is>
       </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>77,25%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>87,16%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>164</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t>117876</t>
-        </is>
-      </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>110080</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>124738</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
-        <is>
-          <t>83,57%</t>
-        </is>
-      </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>78,04%</t>
+          <t>77,44%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>88,43%</t>
+          <t>87,68%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4809,12 +4809,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>230775</t>
+          <t>230389</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>250670</t>
+          <t>251157</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4824,12 +4824,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>79,52%</t>
+          <t>79,38%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>86,37%</t>
+          <t>86,54%</t>
         </is>
       </c>
     </row>
@@ -4842,72 +4842,72 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>33</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>23181</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>16796</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>31315</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>16,43%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>11,91%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>22,2%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>37</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="K17" s="2" t="inlineStr">
         <is>
           <t>25349</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>19155</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>33935</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>18376</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>33660</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
         <is>
           <t>16,99%</t>
         </is>
       </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>12,84%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>22,75%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>33</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>23181</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>16319</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>30977</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
-        <is>
-          <t>16,43%</t>
-        </is>
-      </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>11,57%</t>
+          <t>12,32%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>21,96%</t>
+          <t>22,56%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4922,12 +4922,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>39556</t>
+          <t>39069</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>59451</t>
+          <t>59837</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4937,12 +4937,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>13,63%</t>
+          <t>13,46%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>20,48%</t>
+          <t>20,62%</t>
         </is>
       </c>
     </row>
@@ -4955,57 +4955,57 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>197</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>141057</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>141057</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>141057</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>213</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="K18" s="2" t="inlineStr">
         <is>
           <t>149169</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
+      <c r="L18" s="2" t="inlineStr">
         <is>
           <t>149169</t>
         </is>
       </c>
-      <c r="F18" s="2" t="inlineStr">
+      <c r="M18" s="2" t="inlineStr">
         <is>
           <t>149169</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>197</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="inlineStr">
-        <is>
-          <t>141057</t>
-        </is>
-      </c>
-      <c r="L18" s="2" t="inlineStr">
-        <is>
-          <t>141057</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="inlineStr">
-        <is>
-          <t>141057</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -5072,72 +5072,72 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
+          <t>90</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>62813</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>57378</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>67234</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>84,84%</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>77,5%</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>90,81%</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr">
+        <is>
           <t>67</t>
         </is>
       </c>
-      <c r="D19" s="2" t="inlineStr">
+      <c r="K19" s="2" t="inlineStr">
         <is>
           <t>47993</t>
         </is>
       </c>
-      <c r="E19" s="2" t="inlineStr">
-        <is>
-          <t>43405</t>
-        </is>
-      </c>
-      <c r="F19" s="2" t="inlineStr">
-        <is>
-          <t>51216</t>
-        </is>
-      </c>
-      <c r="G19" s="2" t="inlineStr">
+      <c r="L19" s="2" t="inlineStr">
+        <is>
+          <t>43486</t>
+        </is>
+      </c>
+      <c r="M19" s="2" t="inlineStr">
+        <is>
+          <t>50831</t>
+        </is>
+      </c>
+      <c r="N19" s="2" t="inlineStr">
         <is>
           <t>89,02%</t>
         </is>
       </c>
-      <c r="H19" s="2" t="inlineStr">
-        <is>
-          <t>80,51%</t>
-        </is>
-      </c>
-      <c r="I19" s="2" t="inlineStr">
-        <is>
-          <t>95,0%</t>
-        </is>
-      </c>
-      <c r="J19" s="2" t="inlineStr">
-        <is>
-          <t>90</t>
-        </is>
-      </c>
-      <c r="K19" s="2" t="inlineStr">
-        <is>
-          <t>62813</t>
-        </is>
-      </c>
-      <c r="L19" s="2" t="inlineStr">
-        <is>
-          <t>57095</t>
-        </is>
-      </c>
-      <c r="M19" s="2" t="inlineStr">
-        <is>
-          <t>67173</t>
-        </is>
-      </c>
-      <c r="N19" s="2" t="inlineStr">
-        <is>
-          <t>84,84%</t>
-        </is>
-      </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>77,12%</t>
+          <t>80,66%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>90,73%</t>
+          <t>94,29%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5152,12 +5152,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>103553</t>
+          <t>104272</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>116244</t>
+          <t>116602</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5167,12 +5167,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>80,93%</t>
+          <t>81,5%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>90,85%</t>
+          <t>91,13%</t>
         </is>
       </c>
     </row>
@@ -5185,72 +5185,72 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>11225</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>6804</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>16660</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>15,16%</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>9,19%</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>22,5%</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr">
+        <is>
           <t>9</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
+      <c r="K20" s="2" t="inlineStr">
         <is>
           <t>5918</t>
         </is>
       </c>
-      <c r="E20" s="2" t="inlineStr">
-        <is>
-          <t>2695</t>
-        </is>
-      </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>10506</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="inlineStr">
+      <c r="L20" s="2" t="inlineStr">
+        <is>
+          <t>3080</t>
+        </is>
+      </c>
+      <c r="M20" s="2" t="inlineStr">
+        <is>
+          <t>10425</t>
+        </is>
+      </c>
+      <c r="N20" s="2" t="inlineStr">
         <is>
           <t>10,98%</t>
         </is>
       </c>
-      <c r="H20" s="2" t="inlineStr">
-        <is>
-          <t>5,0%</t>
-        </is>
-      </c>
-      <c r="I20" s="2" t="inlineStr">
-        <is>
-          <t>19,49%</t>
-        </is>
-      </c>
-      <c r="J20" s="2" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
-      </c>
-      <c r="K20" s="2" t="inlineStr">
-        <is>
-          <t>11225</t>
-        </is>
-      </c>
-      <c r="L20" s="2" t="inlineStr">
-        <is>
-          <t>6865</t>
-        </is>
-      </c>
-      <c r="M20" s="2" t="inlineStr">
-        <is>
-          <t>16943</t>
-        </is>
-      </c>
-      <c r="N20" s="2" t="inlineStr">
-        <is>
-          <t>15,16%</t>
-        </is>
-      </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>9,27%</t>
+          <t>5,71%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>22,88%</t>
+          <t>19,34%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5265,12 +5265,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>11705</t>
+          <t>11347</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>24396</t>
+          <t>23677</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5280,12 +5280,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>9,15%</t>
+          <t>8,87%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>19,07%</t>
+          <t>18,5%</t>
         </is>
       </c>
     </row>
@@ -5298,57 +5298,57 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
+          <t>107</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>74038</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>74038</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>74038</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="inlineStr">
+        <is>
           <t>76</t>
         </is>
       </c>
-      <c r="D21" s="2" t="inlineStr">
+      <c r="K21" s="2" t="inlineStr">
         <is>
           <t>53911</t>
         </is>
       </c>
-      <c r="E21" s="2" t="inlineStr">
+      <c r="L21" s="2" t="inlineStr">
         <is>
           <t>53911</t>
         </is>
       </c>
-      <c r="F21" s="2" t="inlineStr">
+      <c r="M21" s="2" t="inlineStr">
         <is>
           <t>53911</t>
-        </is>
-      </c>
-      <c r="G21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J21" s="2" t="inlineStr">
-        <is>
-          <t>107</t>
-        </is>
-      </c>
-      <c r="K21" s="2" t="inlineStr">
-        <is>
-          <t>74038</t>
-        </is>
-      </c>
-      <c r="L21" s="2" t="inlineStr">
-        <is>
-          <t>74038</t>
-        </is>
-      </c>
-      <c r="M21" s="2" t="inlineStr">
-        <is>
-          <t>74038</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -5415,72 +5415,72 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
+          <t>898</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>629662</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>615728</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>644009</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t>87,86%</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t>85,92%</t>
+        </is>
+      </c>
+      <c r="I22" s="2" t="inlineStr">
+        <is>
+          <t>89,87%</t>
+        </is>
+      </c>
+      <c r="J22" s="2" t="inlineStr">
+        <is>
           <t>869</t>
         </is>
       </c>
-      <c r="D22" s="2" t="inlineStr">
+      <c r="K22" s="2" t="inlineStr">
         <is>
           <t>602362</t>
         </is>
       </c>
-      <c r="E22" s="2" t="inlineStr">
-        <is>
-          <t>589342</t>
-        </is>
-      </c>
-      <c r="F22" s="2" t="inlineStr">
-        <is>
-          <t>615289</t>
-        </is>
-      </c>
-      <c r="G22" s="2" t="inlineStr">
+      <c r="L22" s="2" t="inlineStr">
+        <is>
+          <t>586938</t>
+        </is>
+      </c>
+      <c r="M22" s="2" t="inlineStr">
+        <is>
+          <t>614635</t>
+        </is>
+      </c>
+      <c r="N22" s="2" t="inlineStr">
         <is>
           <t>88,77%</t>
         </is>
       </c>
-      <c r="H22" s="2" t="inlineStr">
-        <is>
-          <t>86,85%</t>
-        </is>
-      </c>
-      <c r="I22" s="2" t="inlineStr">
-        <is>
-          <t>90,68%</t>
-        </is>
-      </c>
-      <c r="J22" s="2" t="inlineStr">
-        <is>
-          <t>898</t>
-        </is>
-      </c>
-      <c r="K22" s="2" t="inlineStr">
-        <is>
-          <t>629662</t>
-        </is>
-      </c>
-      <c r="L22" s="2" t="inlineStr">
-        <is>
-          <t>614307</t>
-        </is>
-      </c>
-      <c r="M22" s="2" t="inlineStr">
-        <is>
-          <t>642988</t>
-        </is>
-      </c>
-      <c r="N22" s="2" t="inlineStr">
-        <is>
-          <t>87,86%</t>
-        </is>
-      </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>85,72%</t>
+          <t>86,5%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>89,72%</t>
+          <t>90,58%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -5495,12 +5495,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>1213472</t>
+          <t>1211251</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>1253037</t>
+          <t>1250813</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -5510,12 +5510,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>86,98%</t>
+          <t>86,82%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>89,81%</t>
+          <t>89,65%</t>
         </is>
       </c>
     </row>
@@ -5528,72 +5528,72 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
+          <t>125</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>86971</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>72624</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>100905</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>12,14%</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>10,13%</t>
+        </is>
+      </c>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t>14,08%</t>
+        </is>
+      </c>
+      <c r="J23" s="2" t="inlineStr">
+        <is>
           <t>111</t>
         </is>
       </c>
-      <c r="D23" s="2" t="inlineStr">
+      <c r="K23" s="2" t="inlineStr">
         <is>
           <t>76182</t>
         </is>
       </c>
-      <c r="E23" s="2" t="inlineStr">
-        <is>
-          <t>63255</t>
-        </is>
-      </c>
-      <c r="F23" s="2" t="inlineStr">
-        <is>
-          <t>89202</t>
-        </is>
-      </c>
-      <c r="G23" s="2" t="inlineStr">
+      <c r="L23" s="2" t="inlineStr">
+        <is>
+          <t>63909</t>
+        </is>
+      </c>
+      <c r="M23" s="2" t="inlineStr">
+        <is>
+          <t>91606</t>
+        </is>
+      </c>
+      <c r="N23" s="2" t="inlineStr">
         <is>
           <t>11,23%</t>
         </is>
       </c>
-      <c r="H23" s="2" t="inlineStr">
-        <is>
-          <t>9,32%</t>
-        </is>
-      </c>
-      <c r="I23" s="2" t="inlineStr">
-        <is>
-          <t>13,15%</t>
-        </is>
-      </c>
-      <c r="J23" s="2" t="inlineStr">
-        <is>
-          <t>125</t>
-        </is>
-      </c>
-      <c r="K23" s="2" t="inlineStr">
-        <is>
-          <t>86971</t>
-        </is>
-      </c>
-      <c r="L23" s="2" t="inlineStr">
-        <is>
-          <t>73645</t>
-        </is>
-      </c>
-      <c r="M23" s="2" t="inlineStr">
-        <is>
-          <t>102326</t>
-        </is>
-      </c>
-      <c r="N23" s="2" t="inlineStr">
-        <is>
-          <t>12,14%</t>
-        </is>
-      </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>10,28%</t>
+          <t>9,42%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>14,28%</t>
+          <t>13,5%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -5608,12 +5608,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>142140</t>
+          <t>144364</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>181705</t>
+          <t>183926</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -5623,12 +5623,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>10,19%</t>
+          <t>10,35%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>13,02%</t>
+          <t>13,18%</t>
         </is>
       </c>
     </row>
@@ -5641,57 +5641,57 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
+          <t>1023</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>716633</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>716633</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>716633</t>
+        </is>
+      </c>
+      <c r="G24" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H24" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I24" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J24" s="2" t="inlineStr">
+        <is>
           <t>980</t>
         </is>
       </c>
-      <c r="D24" s="2" t="inlineStr">
+      <c r="K24" s="2" t="inlineStr">
         <is>
           <t>678544</t>
         </is>
       </c>
-      <c r="E24" s="2" t="inlineStr">
+      <c r="L24" s="2" t="inlineStr">
         <is>
           <t>678544</t>
         </is>
       </c>
-      <c r="F24" s="2" t="inlineStr">
+      <c r="M24" s="2" t="inlineStr">
         <is>
           <t>678544</t>
-        </is>
-      </c>
-      <c r="G24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J24" s="2" t="inlineStr">
-        <is>
-          <t>1023</t>
-        </is>
-      </c>
-      <c r="K24" s="2" t="inlineStr">
-        <is>
-          <t>716633</t>
-        </is>
-      </c>
-      <c r="L24" s="2" t="inlineStr">
-        <is>
-          <t>716633</t>
-        </is>
-      </c>
-      <c r="M24" s="2" t="inlineStr">
-        <is>
-          <t>716633</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -5813,7 +5813,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -5824,7 +5824,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -5992,72 +5992,72 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>129</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>88043</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>81668</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>92580</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>88,22%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>81,83%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>92,77%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>108</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
         <is>
           <t>70960</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>64540</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>75958</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>65032</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>75826</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>85,4%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>77,67%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>91,42%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>129</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>88043</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>82025</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>92881</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>88,22%</t>
-        </is>
-      </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>82,19%</t>
+          <t>78,27%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>93,07%</t>
+          <t>91,26%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6072,12 +6072,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>150895</t>
+          <t>150716</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>165850</t>
+          <t>165712</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -6087,12 +6087,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>82,51%</t>
+          <t>82,41%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>90,68%</t>
+          <t>90,61%</t>
         </is>
       </c>
     </row>
@@ -6105,72 +6105,72 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>11754</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>7217</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>18129</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>11,78%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>7,23%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>18,17%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>18</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>12130</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>7132</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>18550</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>7264</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>18058</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>14,6%</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>8,58%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>22,33%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>11754</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>6916</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>17772</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>11,78%</t>
-        </is>
-      </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>6,93%</t>
+          <t>8,74%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>17,81%</t>
+          <t>21,73%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -6185,12 +6185,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>17037</t>
+          <t>17175</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>31992</t>
+          <t>32171</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -6200,12 +6200,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>9,32%</t>
+          <t>9,39%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>17,49%</t>
+          <t>17,59%</t>
         </is>
       </c>
     </row>
@@ -6218,57 +6218,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>145</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>99797</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>99797</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>99797</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>126</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>83090</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
         <is>
           <t>83090</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="M6" s="2" t="inlineStr">
         <is>
           <t>83090</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>145</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>99797</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>99797</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>99797</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -6335,72 +6335,72 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>145</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>98433</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>91478</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>103525</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>87,81%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>81,61%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>92,36%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>128</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="K7" s="2" t="inlineStr">
         <is>
           <t>86053</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>79275</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>91896</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>78655</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>91738</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
         <is>
           <t>82,1%</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>75,63%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>87,68%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>145</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>98433</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>91844</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>103721</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>87,81%</t>
-        </is>
-      </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>81,94%</t>
+          <t>75,04%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>92,53%</t>
+          <t>87,52%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -6415,12 +6415,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>174525</t>
+          <t>174714</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>192398</t>
+          <t>191997</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -6430,12 +6430,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>80,46%</t>
+          <t>80,55%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>88,7%</t>
+          <t>88,52%</t>
         </is>
       </c>
     </row>
@@ -6448,72 +6448,72 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>13660</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>8568</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>20615</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>12,19%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>7,64%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>18,39%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>27</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>18761</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>12918</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>25539</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>13076</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>26159</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
         <is>
           <t>17,9%</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>12,32%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>24,37%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>19</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>13660</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>8372</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>20249</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>12,19%</t>
-        </is>
-      </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>7,47%</t>
+          <t>12,48%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>18,06%</t>
+          <t>24,96%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -6528,12 +6528,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>24509</t>
+          <t>24910</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>42382</t>
+          <t>42193</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -6543,12 +6543,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>11,3%</t>
+          <t>11,48%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>19,54%</t>
+          <t>19,45%</t>
         </is>
       </c>
     </row>
@@ -6561,57 +6561,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>164</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>112093</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>112093</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>112093</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>155</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>104814</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
         <is>
           <t>104814</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="M9" s="2" t="inlineStr">
         <is>
           <t>104814</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>164</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>112093</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>112093</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>112093</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -6678,72 +6678,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>102</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>69361</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>64700</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>72563</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>91,96%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>85,78%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>96,2%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>88</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="K10" s="2" t="inlineStr">
         <is>
           <t>56958</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>52323</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>59793</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>52255</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>59712</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>92,11%</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>84,61%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>96,69%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>102</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>69361</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>64432</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>72649</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>91,96%</t>
-        </is>
-      </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>85,42%</t>
+          <t>84,5%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>96,32%</t>
+          <t>96,56%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -6758,12 +6758,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>119579</t>
+          <t>119753</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>130402</t>
+          <t>130789</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -6773,12 +6773,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>87,11%</t>
+          <t>87,24%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>95,0%</t>
+          <t>95,28%</t>
         </is>
       </c>
     </row>
@@ -6791,72 +6791,72 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>6067</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>2865</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>10728</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>8,04%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>3,8%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>14,22%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>7</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>4882</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>2047</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>9517</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>2128</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>9585</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
         <is>
           <t>7,89%</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>3,31%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>15,39%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>6067</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>2779</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>10996</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>8,04%</t>
-        </is>
-      </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>3,68%</t>
+          <t>3,44%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>14,58%</t>
+          <t>15,5%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -6871,12 +6871,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>6866</t>
+          <t>6479</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>17689</t>
+          <t>17515</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -6886,12 +6886,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>5,0%</t>
+          <t>4,72%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>12,89%</t>
+          <t>12,76%</t>
         </is>
       </c>
     </row>
@@ -6904,57 +6904,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>111</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>75428</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>75428</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>75428</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>95</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>61840</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
         <is>
           <t>61840</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="M12" s="2" t="inlineStr">
         <is>
           <t>61840</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>111</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>75428</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>75428</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>75428</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -7021,72 +7021,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>248</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>174497</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>165563</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>182993</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>83,01%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>78,76%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>87,05%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>280</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="K13" s="2" t="inlineStr">
         <is>
           <t>182874</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>172190</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>191212</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>173147</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>191460</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>81,79%</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>77,02%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>85,52%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>248</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>174497</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>165371</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>182993</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>83,01%</t>
-        </is>
-      </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>78,67%</t>
+          <t>77,44%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>87,05%</t>
+          <t>85,63%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7101,12 +7101,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>344719</t>
+          <t>343277</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>369307</t>
+          <t>369676</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -7116,12 +7116,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>79,47%</t>
+          <t>79,13%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>85,13%</t>
+          <t>85,22%</t>
         </is>
       </c>
     </row>
@@ -7134,72 +7134,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>35723</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>27227</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>44657</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>16,99%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>12,95%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>21,24%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>61</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>40703</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>32365</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>51387</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>32117</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>50430</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>18,21%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>14,48%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>22,98%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>52</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>35723</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>27227</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>44849</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>16,99%</t>
-        </is>
-      </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>12,95%</t>
+          <t>14,37%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>21,33%</t>
+          <t>22,56%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -7214,12 +7214,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>64490</t>
+          <t>64121</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>89078</t>
+          <t>90520</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -7229,12 +7229,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>14,87%</t>
+          <t>14,78%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>20,53%</t>
+          <t>20,87%</t>
         </is>
       </c>
     </row>
@@ -7247,57 +7247,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>300</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>210220</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>210220</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>210220</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>341</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>223577</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>223577</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>223577</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>300</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>210220</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>210220</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>210220</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -7364,72 +7364,72 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>161</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>116634</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>108618</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>124342</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>81,51%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>75,91%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>86,9%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>173</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="K16" s="2" t="inlineStr">
         <is>
           <t>112825</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>104622</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>119723</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>104446</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>119360</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
         <is>
           <t>82,84%</t>
         </is>
       </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>76,82%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>87,91%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>161</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t>116634</t>
-        </is>
-      </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>107354</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>123456</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
-        <is>
-          <t>81,51%</t>
-        </is>
-      </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>75,03%</t>
+          <t>76,69%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>86,28%</t>
+          <t>87,64%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -7444,12 +7444,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>218573</t>
+          <t>218453</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>239026</t>
+          <t>240586</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -7459,12 +7459,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>78,26%</t>
+          <t>78,22%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>85,59%</t>
+          <t>86,14%</t>
         </is>
       </c>
     </row>
@@ -7477,72 +7477,72 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>37</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>26454</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>18746</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>34470</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>18,49%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>13,1%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>24,09%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>33</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="K17" s="2" t="inlineStr">
         <is>
           <t>23369</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>16471</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>31572</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>16834</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>31748</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
         <is>
           <t>17,16%</t>
         </is>
       </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>12,09%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>23,18%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>37</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>26454</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>19632</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>35734</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
-        <is>
-          <t>18,49%</t>
-        </is>
-      </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>13,72%</t>
+          <t>12,36%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>24,97%</t>
+          <t>23,31%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -7557,12 +7557,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>40256</t>
+          <t>38696</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>60709</t>
+          <t>60829</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -7572,12 +7572,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>14,41%</t>
+          <t>13,86%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>21,74%</t>
+          <t>21,78%</t>
         </is>
       </c>
     </row>
@@ -7590,57 +7590,57 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>198</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>143088</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>143088</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>143088</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>206</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="K18" s="2" t="inlineStr">
         <is>
           <t>136194</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
+      <c r="L18" s="2" t="inlineStr">
         <is>
           <t>136194</t>
         </is>
       </c>
-      <c r="F18" s="2" t="inlineStr">
+      <c r="M18" s="2" t="inlineStr">
         <is>
           <t>136194</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>198</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="inlineStr">
-        <is>
-          <t>143088</t>
-        </is>
-      </c>
-      <c r="L18" s="2" t="inlineStr">
-        <is>
-          <t>143088</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="inlineStr">
-        <is>
-          <t>143088</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -7707,72 +7707,72 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
+          <t>67</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>46634</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>40227</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>52498</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>68,76%</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>59,31%</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>77,4%</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr">
+        <is>
           <t>74</t>
         </is>
       </c>
-      <c r="D19" s="2" t="inlineStr">
+      <c r="K19" s="2" t="inlineStr">
         <is>
           <t>51094</t>
         </is>
       </c>
-      <c r="E19" s="2" t="inlineStr">
-        <is>
-          <t>46005</t>
-        </is>
-      </c>
-      <c r="F19" s="2" t="inlineStr">
-        <is>
-          <t>55031</t>
-        </is>
-      </c>
-      <c r="G19" s="2" t="inlineStr">
+      <c r="L19" s="2" t="inlineStr">
+        <is>
+          <t>45754</t>
+        </is>
+      </c>
+      <c r="M19" s="2" t="inlineStr">
+        <is>
+          <t>55335</t>
+        </is>
+      </c>
+      <c r="N19" s="2" t="inlineStr">
         <is>
           <t>83,64%</t>
         </is>
       </c>
-      <c r="H19" s="2" t="inlineStr">
-        <is>
-          <t>75,31%</t>
-        </is>
-      </c>
-      <c r="I19" s="2" t="inlineStr">
-        <is>
-          <t>90,09%</t>
-        </is>
-      </c>
-      <c r="J19" s="2" t="inlineStr">
-        <is>
-          <t>67</t>
-        </is>
-      </c>
-      <c r="K19" s="2" t="inlineStr">
-        <is>
-          <t>46634</t>
-        </is>
-      </c>
-      <c r="L19" s="2" t="inlineStr">
-        <is>
-          <t>40277</t>
-        </is>
-      </c>
-      <c r="M19" s="2" t="inlineStr">
-        <is>
-          <t>52880</t>
-        </is>
-      </c>
-      <c r="N19" s="2" t="inlineStr">
-        <is>
-          <t>68,76%</t>
-        </is>
-      </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>59,38%</t>
+          <t>74,9%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>77,97%</t>
+          <t>90,58%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -7787,12 +7787,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>88008</t>
+          <t>89455</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>105003</t>
+          <t>105083</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -7802,12 +7802,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>68,27%</t>
+          <t>69,39%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>81,45%</t>
+          <t>81,52%</t>
         </is>
       </c>
     </row>
@@ -7820,72 +7820,72 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>21191</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>15327</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>27598</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>31,24%</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>22,6%</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>40,69%</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr">
+        <is>
           <t>15</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
+      <c r="K20" s="2" t="inlineStr">
         <is>
           <t>9993</t>
         </is>
       </c>
-      <c r="E20" s="2" t="inlineStr">
-        <is>
-          <t>6056</t>
-        </is>
-      </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>15082</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="inlineStr">
+      <c r="L20" s="2" t="inlineStr">
+        <is>
+          <t>5752</t>
+        </is>
+      </c>
+      <c r="M20" s="2" t="inlineStr">
+        <is>
+          <t>15333</t>
+        </is>
+      </c>
+      <c r="N20" s="2" t="inlineStr">
         <is>
           <t>16,36%</t>
         </is>
       </c>
-      <c r="H20" s="2" t="inlineStr">
-        <is>
-          <t>9,91%</t>
-        </is>
-      </c>
-      <c r="I20" s="2" t="inlineStr">
-        <is>
-          <t>24,69%</t>
-        </is>
-      </c>
-      <c r="J20" s="2" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="K20" s="2" t="inlineStr">
-        <is>
-          <t>21191</t>
-        </is>
-      </c>
-      <c r="L20" s="2" t="inlineStr">
-        <is>
-          <t>14945</t>
-        </is>
-      </c>
-      <c r="M20" s="2" t="inlineStr">
-        <is>
-          <t>27548</t>
-        </is>
-      </c>
-      <c r="N20" s="2" t="inlineStr">
-        <is>
-          <t>31,24%</t>
-        </is>
-      </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>22,03%</t>
+          <t>9,42%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>40,62%</t>
+          <t>25,1%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -7900,12 +7900,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>23909</t>
+          <t>23829</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>40904</t>
+          <t>39457</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -7915,12 +7915,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>18,55%</t>
+          <t>18,48%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>31,73%</t>
+          <t>30,61%</t>
         </is>
       </c>
     </row>
@@ -7933,57 +7933,57 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
+          <t>97</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>67825</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>67825</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>67825</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="inlineStr">
+        <is>
           <t>89</t>
         </is>
       </c>
-      <c r="D21" s="2" t="inlineStr">
+      <c r="K21" s="2" t="inlineStr">
         <is>
           <t>61087</t>
         </is>
       </c>
-      <c r="E21" s="2" t="inlineStr">
+      <c r="L21" s="2" t="inlineStr">
         <is>
           <t>61087</t>
         </is>
       </c>
-      <c r="F21" s="2" t="inlineStr">
+      <c r="M21" s="2" t="inlineStr">
         <is>
           <t>61087</t>
-        </is>
-      </c>
-      <c r="G21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J21" s="2" t="inlineStr">
-        <is>
-          <t>97</t>
-        </is>
-      </c>
-      <c r="K21" s="2" t="inlineStr">
-        <is>
-          <t>67825</t>
-        </is>
-      </c>
-      <c r="L21" s="2" t="inlineStr">
-        <is>
-          <t>67825</t>
-        </is>
-      </c>
-      <c r="M21" s="2" t="inlineStr">
-        <is>
-          <t>67825</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -8050,72 +8050,72 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
+          <t>852</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>593602</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>576598</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>610600</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t>83,79%</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t>81,39%</t>
+        </is>
+      </c>
+      <c r="I22" s="2" t="inlineStr">
+        <is>
+          <t>86,19%</t>
+        </is>
+      </c>
+      <c r="J22" s="2" t="inlineStr">
+        <is>
           <t>851</t>
         </is>
       </c>
-      <c r="D22" s="2" t="inlineStr">
+      <c r="K22" s="2" t="inlineStr">
         <is>
           <t>560763</t>
         </is>
       </c>
-      <c r="E22" s="2" t="inlineStr">
-        <is>
-          <t>543778</t>
-        </is>
-      </c>
-      <c r="F22" s="2" t="inlineStr">
-        <is>
-          <t>574371</t>
-        </is>
-      </c>
-      <c r="G22" s="2" t="inlineStr">
+      <c r="L22" s="2" t="inlineStr">
+        <is>
+          <t>544087</t>
+        </is>
+      </c>
+      <c r="M22" s="2" t="inlineStr">
+        <is>
+          <t>574952</t>
+        </is>
+      </c>
+      <c r="N22" s="2" t="inlineStr">
         <is>
           <t>83,62%</t>
         </is>
       </c>
-      <c r="H22" s="2" t="inlineStr">
-        <is>
-          <t>81,09%</t>
-        </is>
-      </c>
-      <c r="I22" s="2" t="inlineStr">
-        <is>
-          <t>85,65%</t>
-        </is>
-      </c>
-      <c r="J22" s="2" t="inlineStr">
-        <is>
-          <t>852</t>
-        </is>
-      </c>
-      <c r="K22" s="2" t="inlineStr">
-        <is>
-          <t>593602</t>
-        </is>
-      </c>
-      <c r="L22" s="2" t="inlineStr">
-        <is>
-          <t>576864</t>
-        </is>
-      </c>
-      <c r="M22" s="2" t="inlineStr">
-        <is>
-          <t>609141</t>
-        </is>
-      </c>
-      <c r="N22" s="2" t="inlineStr">
-        <is>
-          <t>83,79%</t>
-        </is>
-      </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>81,43%</t>
+          <t>81,13%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>85,98%</t>
+          <t>85,74%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -8130,12 +8130,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>1128903</t>
+          <t>1130955</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>1174827</t>
+          <t>1178282</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -8145,12 +8145,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>81,86%</t>
+          <t>82,01%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>85,19%</t>
+          <t>85,44%</t>
         </is>
       </c>
     </row>
@@ -8163,72 +8163,72 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
+          <t>163</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>114849</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>97851</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>131853</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>16,21%</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>13,81%</t>
+        </is>
+      </c>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t>18,61%</t>
+        </is>
+      </c>
+      <c r="J23" s="2" t="inlineStr">
+        <is>
           <t>161</t>
         </is>
       </c>
-      <c r="D23" s="2" t="inlineStr">
+      <c r="K23" s="2" t="inlineStr">
         <is>
           <t>109838</t>
         </is>
       </c>
-      <c r="E23" s="2" t="inlineStr">
-        <is>
-          <t>96230</t>
-        </is>
-      </c>
-      <c r="F23" s="2" t="inlineStr">
-        <is>
-          <t>126823</t>
-        </is>
-      </c>
-      <c r="G23" s="2" t="inlineStr">
+      <c r="L23" s="2" t="inlineStr">
+        <is>
+          <t>95649</t>
+        </is>
+      </c>
+      <c r="M23" s="2" t="inlineStr">
+        <is>
+          <t>126514</t>
+        </is>
+      </c>
+      <c r="N23" s="2" t="inlineStr">
         <is>
           <t>16,38%</t>
         </is>
       </c>
-      <c r="H23" s="2" t="inlineStr">
-        <is>
-          <t>14,35%</t>
-        </is>
-      </c>
-      <c r="I23" s="2" t="inlineStr">
-        <is>
-          <t>18,91%</t>
-        </is>
-      </c>
-      <c r="J23" s="2" t="inlineStr">
-        <is>
-          <t>163</t>
-        </is>
-      </c>
-      <c r="K23" s="2" t="inlineStr">
-        <is>
-          <t>114849</t>
-        </is>
-      </c>
-      <c r="L23" s="2" t="inlineStr">
-        <is>
-          <t>99310</t>
-        </is>
-      </c>
-      <c r="M23" s="2" t="inlineStr">
-        <is>
-          <t>131587</t>
-        </is>
-      </c>
-      <c r="N23" s="2" t="inlineStr">
-        <is>
-          <t>16,21%</t>
-        </is>
-      </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>14,02%</t>
+          <t>14,26%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>18,57%</t>
+          <t>18,87%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -8243,12 +8243,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>204225</t>
+          <t>200770</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>250149</t>
+          <t>248097</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -8258,12 +8258,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>14,81%</t>
+          <t>14,56%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>18,14%</t>
+          <t>17,99%</t>
         </is>
       </c>
     </row>
@@ -8276,57 +8276,57 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
+          <t>1015</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>708451</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>708451</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>708451</t>
+        </is>
+      </c>
+      <c r="G24" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H24" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I24" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J24" s="2" t="inlineStr">
+        <is>
           <t>1012</t>
         </is>
       </c>
-      <c r="D24" s="2" t="inlineStr">
+      <c r="K24" s="2" t="inlineStr">
         <is>
           <t>670601</t>
         </is>
       </c>
-      <c r="E24" s="2" t="inlineStr">
+      <c r="L24" s="2" t="inlineStr">
         <is>
           <t>670601</t>
         </is>
       </c>
-      <c r="F24" s="2" t="inlineStr">
+      <c r="M24" s="2" t="inlineStr">
         <is>
           <t>670601</t>
-        </is>
-      </c>
-      <c r="G24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J24" s="2" t="inlineStr">
-        <is>
-          <t>1015</t>
-        </is>
-      </c>
-      <c r="K24" s="2" t="inlineStr">
-        <is>
-          <t>708451</t>
-        </is>
-      </c>
-      <c r="L24" s="2" t="inlineStr">
-        <is>
-          <t>708451</t>
-        </is>
-      </c>
-      <c r="M24" s="2" t="inlineStr">
-        <is>
-          <t>708451</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
